--- a/arquivos_auxiliares/dotacoes.xlsx
+++ b/arquivos_auxiliares/dotacoes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nathan Faita\Documents\GitHub\sof_adesampa\arquivos_auxiliares\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A0CC00B-97FF-47F2-A93B-52FFF87286DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{310775E1-2CB4-47B3-8B76-087FC052942F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E33505D4-253B-4815-8B22-C3EA0577A6FD}"/>
+    <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15750" xr2:uid="{E33505D4-253B-4815-8B22-C3EA0577A6FD}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="74">
   <si>
     <t>secretaria</t>
   </si>
@@ -258,6 +258,9 @@
   </si>
   <si>
     <t>33903900</t>
+  </si>
+  <si>
+    <t>SMDET - ADE SAMPA</t>
   </si>
 </sst>
 </file>
@@ -370,22 +373,22 @@
   <autoFilter ref="A1:R8" xr:uid="{D6DDDE7D-2EBF-4837-BBCF-EC98433F9477}"/>
   <tableColumns count="18">
     <tableColumn id="1" xr3:uid="{23C99B1D-A5AE-4386-9D63-CAFB4A69DD86}" name="contrato_gestao" dataDxfId="16"/>
-    <tableColumn id="17" xr3:uid="{4F2DCCA8-140A-4098-A904-8ABB274E5CFB}" name="secretaria" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{79146E5E-8433-4E94-B6FF-99155643BDFF}" name="orgao" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{2D94C541-87F8-4C37-BD89-31E5CB7C16CA}" name="uo" dataDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{590FC0E5-789D-4F73-98EA-6CE3F63396E4}" name="funcao" dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{54C2400F-43F6-4C02-82CC-884A0FB0F524}" name="subfuncao" dataDxfId="12"/>
-    <tableColumn id="6" xr3:uid="{6D2CDCD6-BA50-48FE-89B3-8CB25EDF8540}" name="programa" dataDxfId="11"/>
-    <tableColumn id="7" xr3:uid="{094B3C07-A6FA-4658-8287-B370E25F0483}" name="proj_ativ" dataDxfId="10"/>
-    <tableColumn id="8" xr3:uid="{D1C277B1-12AC-44EE-882C-CF8010E502E8}" name="categoria" dataDxfId="9"/>
-    <tableColumn id="9" xr3:uid="{B80673DD-D9A7-4443-AE12-90A2308EC869}" name="grupo" dataDxfId="8"/>
-    <tableColumn id="10" xr3:uid="{DFB2D1EE-3CFC-4BD2-A720-7930BF8C98D8}" name="modalidade" dataDxfId="7"/>
-    <tableColumn id="11" xr3:uid="{A55D7E17-81E9-4FAD-B901-A2BBEAFADFAD}" name="elemento" dataDxfId="6"/>
-    <tableColumn id="12" xr3:uid="{98A9ECAD-C81A-4566-8F91-E36A0033A941}" name="fonte" dataDxfId="5"/>
-    <tableColumn id="18" xr3:uid="{D86AEE5C-3B33-4534-9363-BFB57755A948}" name="despesa" dataDxfId="0"/>
-    <tableColumn id="13" xr3:uid="{CE9C1543-D8E3-4FD3-BDEF-DAE7B4CD1B6A}" name="referencia" dataDxfId="4"/>
-    <tableColumn id="14" xr3:uid="{F729137D-E264-4515-9B56-55379DD3F246}" name="destinacao" dataDxfId="3"/>
-    <tableColumn id="15" xr3:uid="{DD0A0178-B0DD-41AB-9F29-F20B903A398B}" name="vinculacao" dataDxfId="2"/>
+    <tableColumn id="17" xr3:uid="{4F2DCCA8-140A-4098-A904-8ABB274E5CFB}" name="secretaria" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{79146E5E-8433-4E94-B6FF-99155643BDFF}" name="orgao" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{2D94C541-87F8-4C37-BD89-31E5CB7C16CA}" name="uo" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{590FC0E5-789D-4F73-98EA-6CE3F63396E4}" name="funcao" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{54C2400F-43F6-4C02-82CC-884A0FB0F524}" name="subfuncao" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{6D2CDCD6-BA50-48FE-89B3-8CB25EDF8540}" name="programa" dataDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{094B3C07-A6FA-4658-8287-B370E25F0483}" name="proj_ativ" dataDxfId="9"/>
+    <tableColumn id="8" xr3:uid="{D1C277B1-12AC-44EE-882C-CF8010E502E8}" name="categoria" dataDxfId="8"/>
+    <tableColumn id="9" xr3:uid="{B80673DD-D9A7-4443-AE12-90A2308EC869}" name="grupo" dataDxfId="7"/>
+    <tableColumn id="10" xr3:uid="{DFB2D1EE-3CFC-4BD2-A720-7930BF8C98D8}" name="modalidade" dataDxfId="6"/>
+    <tableColumn id="11" xr3:uid="{A55D7E17-81E9-4FAD-B901-A2BBEAFADFAD}" name="elemento" dataDxfId="5"/>
+    <tableColumn id="12" xr3:uid="{98A9ECAD-C81A-4566-8F91-E36A0033A941}" name="fonte" dataDxfId="4"/>
+    <tableColumn id="18" xr3:uid="{D86AEE5C-3B33-4534-9363-BFB57755A948}" name="despesa" dataDxfId="3"/>
+    <tableColumn id="13" xr3:uid="{CE9C1543-D8E3-4FD3-BDEF-DAE7B4CD1B6A}" name="referencia" dataDxfId="2"/>
+    <tableColumn id="14" xr3:uid="{F729137D-E264-4515-9B56-55379DD3F246}" name="destinacao" dataDxfId="1"/>
+    <tableColumn id="15" xr3:uid="{DD0A0178-B0DD-41AB-9F29-F20B903A398B}" name="vinculacao" dataDxfId="0"/>
     <tableColumn id="16" xr3:uid="{38B7480B-9F6D-4338-811C-0549575D2669}" name="dotacao_exclusiva"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -785,7 +788,7 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>27</v>
